--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,6 +2545,44 @@
       </c>
       <c r="F56" t="n">
         <v>2495.97607421875</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2522.330078125</v>
+      </c>
+      <c r="H56" t="n">
+        <v>26.35400390625</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.04482772238281</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.068795814594038</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:18</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2515.265625</v>
       </c>
     </row>
   </sheetData>
@@ -2558,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5949,6 +5987,24 @@
           <t>2508.615723,2498.887207,2500.500488,2491.285400,2500.025146,2495.976074</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2536.090088,2534.510010,2518.919922,2525.350098,2520.159912,2522.330078</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>27.474365,35.622803,18.419434,34.064698,20.134766,26.354004</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1.083336,1.405510,0.731243,1.348910,0.798948,1.044828</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1.068795814594038</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>2497.724121,2494.609619,2486.855957,2484.924072,2498.440918,2479.211182</t>
@@ -5962,6 +6018,49 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>2488.045898,2474.351318,2479.416504,2468.171875,2478.136475,2467.635742</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:18</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2517.475586,2514.220215,2513.427734,2513.249512,2513.835938,2515.265625</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2514.126953,2510.671387,2512.767578,2505.310059,2518.631348,2510.441406</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2494.535156,2484.434570,2478.120117,2475.971680,2472.627930,2467.858398</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2503.724609,2495.843262,2494.279785,2492.883789,2493.726074,2490.635742</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2583,44 @@
       </c>
       <c r="F57" t="n">
         <v>2515.265625</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2513.590087890625</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.675537109375</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.06665912303867695</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.7382763261502934</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:39</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2514.58349609375</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6048,6 +6086,24 @@
           <t>2517.475586,2514.220215,2513.427734,2513.249512,2513.835938,2515.265625</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2480.790039,2490.199951,2505.219971,2475.879883,2511.760010,2513.590088</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>36.685547,24.020264,8.207763,37.369629,2.075928,1.675537</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1.478785,0.964592,0.327626,1.509347,0.082648,0.066659</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.7382763261502934</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>2514.126953,2510.671387,2512.767578,2505.310059,2518.631348,2510.441406</t>
@@ -6061,6 +6117,49 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>2503.724609,2495.843262,2494.279785,2492.883789,2493.726074,2490.635742</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:39</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2502.871582,2498.915771,2506.475098,2505.761230,2514.647461,2514.583496</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2502.543945,2499.767822,2485.854492,2489.609863,2503.704834,2500.809570</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2471.506836,2456.304932,2461.908691,2458.479004,2461.571777,2452.031250</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2480.716797,2477.628662,2490.312500,2486.984619,2494.234375,2484.448975</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,6 +2621,44 @@
       </c>
       <c r="F58" t="n">
         <v>2514.58349609375</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2489.669921875</v>
+      </c>
+      <c r="H58" t="n">
+        <v>24.91357421875</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.000677800693647</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.6516855336820684</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:38:07</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2489.08544921875</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6147,6 +6185,24 @@
           <t>2502.871582,2498.915771,2506.475098,2505.761230,2514.647461,2514.583496</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2508.060059,2507.570068,2539.520020,2515.780029,2498.209961,2489.669922</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>5.188477,8.654297,33.044922,10.018799,16.437500,24.913574</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.206872,0.345127,1.301227,0.398238,0.657971,1.000678</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.6516855336820684</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>2502.543945,2499.767822,2485.854492,2489.609863,2503.704834,2500.809570</t>
@@ -6160,6 +6216,49 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>2480.716797,2477.628662,2490.312500,2486.984619,2494.234375,2484.448975</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:38:07</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2483.522461,2489.098633,2486.228760,2485.330078,2489.497559,2489.085449</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2485.730713,2476.376221,2481.356689,2474.876221,2488.878174,2471.809814</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2448.895020,2451.381592,2435.429199,2424.508301,2432.032471,2421.919189</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2458.479004,2471.783936,2462.275146,2462.181396,2463.527344,2460.730225</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,44 @@
       </c>
       <c r="F59" t="n">
         <v>2489.08544921875</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2401.169921875</v>
+      </c>
+      <c r="H59" t="n">
+        <v>87.91552734375</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3.661362177779549</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.856069197561832</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:22</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2411.310546875</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6246,6 +6284,24 @@
           <t>2483.522461,2489.098633,2486.228760,2485.330078,2489.497559,2489.085449</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2475.350098,2423.199951,2414.330078,2396.139893,2400.090088,2401.169922</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>8.172363,65.898682,71.898682,89.190185,89.407471,87.915527</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.330150,2.719490,2.977997,3.722245,3.725171,3.661362</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>2.856069197561832</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>2485.730713,2476.376221,2481.356689,2474.876221,2488.878174,2471.809814</t>
@@ -6259,6 +6315,49 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>2458.479004,2471.783936,2462.275146,2462.181396,2463.527344,2460.730225</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:22</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2393.226562,2395.312988,2400.617188,2403.159668,2410.879395,2411.310547</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2389.054199,2395.274414,2393.606934,2396.977051,2405.898926,2401.783691</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2353.934814,2341.738770,2335.642578,2322.248047,2323.533691,2314.914551</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2371.986328,2368.298828,2366.412109,2363.113770,2364.167969,2358.811523</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,44 @@
       </c>
       <c r="F60" t="n">
         <v>2411.310546875</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2429.1298828125</v>
+      </c>
+      <c r="H60" t="n">
+        <v>17.8193359375</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.7335686767340897</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.632732505787001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:45</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2436.572021484375</v>
       </c>
     </row>
   </sheetData>
@@ -2710,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6345,6 +6383,24 @@
           <t>2393.226562,2395.312988,2400.617188,2403.159668,2410.879395,2411.310547</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2420.760010,2391.290039,2407.389893,2416.449951,2433.409912,2429.129883</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>27.533448,4.022949,6.772705,13.290283,22.530517,17.819336</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1.137389,0.168233,0.281330,0.549992,0.925883,0.733569</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.632732505787001</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>2389.054199,2395.274414,2393.606934,2396.977051,2405.898926,2401.783691</t>
@@ -6358,6 +6414,49 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>2371.986328,2368.298828,2366.412109,2363.113770,2364.167969,2358.811523</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:45</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2429.381836,2429.361328,2431.983643,2432.460693,2437.432129,2436.572021</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2431.630371,2428.415283,2433.851562,2433.851562,2434.428711,2434.309326</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2402.456543,2396.724365,2393.810791,2385.438477,2389.198975,2384.141846</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2411.913086,2409.691895,2408.082520,2406.668945,2407.706787,2405.620850</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2735,6 +2735,44 @@
       </c>
       <c r="F61" t="n">
         <v>2436.572021484375</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2470.97998046875</v>
+      </c>
+      <c r="H61" t="n">
+        <v>34.407958984375</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.392482304848449</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.025642317093593</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:24:02</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2459.9072265625</v>
       </c>
     </row>
   </sheetData>
@@ -2748,7 +2786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6444,6 +6482,24 @@
           <t>2429.381836,2429.361328,2431.983643,2432.460693,2437.432129,2436.572021</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2440.199951,2467.989990,2447.340088,2445.439941,2476.929932,2470.979980</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>10.818115,38.628662,15.356445,12.979248,39.497803,34.407959</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.443329,1.565187,0.627475,0.530753,1.594627,1.392482</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>1.025642317093593</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>2431.630371,2428.415283,2433.851562,2433.851562,2434.428711,2434.309326</t>
@@ -6457,6 +6513,49 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>2411.913086,2409.691895,2408.082520,2406.668945,2407.706787,2405.620850</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:24:02</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2466.754395,2464.408691,2464.164551,2463.335449,2461.402344,2459.907227</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2464.562256,2460.438721,2461.214355,2459.763916,2456.958252,2454.214355</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2440.024170,2427.937988,2420.437012,2411.137207,2405.079834,2396.682129</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2449.209473,2443.104492,2436.833984,2432.735840,2425.008301,2421.646973</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,6 +2773,44 @@
       </c>
       <c r="F62" t="n">
         <v>2459.9072265625</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2621.5400390625</v>
+      </c>
+      <c r="H62" t="n">
+        <v>161.6328125</v>
+      </c>
+      <c r="I62" t="n">
+        <v>6.165567189193196</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5.094561523381345</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:53</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2572.839599609375</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,6 +6581,24 @@
           <t>2466.754395,2464.408691,2464.164551,2463.335449,2461.402344,2459.907227</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2505.800049,2583.219971,2636.800049,2611.340088,2619.330078,2621.540039</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>39.045654,118.811280,172.635498,148.004639,157.927734,161.632812</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1.558211,4.599348,6.547159,5.667766,6.029318,6.165567</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>5.094561523381345</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>2464.562256,2460.438721,2461.214355,2459.763916,2456.958252,2454.214355</t>
@@ -6556,6 +6612,49 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>2449.209473,2443.104492,2436.833984,2432.735840,2425.008301,2421.646973</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:53</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2616.583740,2608.386475,2600.903809,2590.127197,2580.098389,2572.839600</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2612.286377,2600.650391,2595.527588,2582.640869,2568.953125,2562.366699</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2579.241699,2559.368408,2541.126953,2519.934082,2501.810547,2488.346924</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2594.654053,2578.917725,2563.359619,2547.539795,2531.041992,2519.468994</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2811,6 +2811,44 @@
       </c>
       <c r="F63" t="n">
         <v>2572.839599609375</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2584.969970703125</v>
+      </c>
+      <c r="H63" t="n">
+        <v>12.13037109375</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.4692654549658261</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.9529371244949153</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:40:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2563.86474609375</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6642,6 +6680,24 @@
           <t>2616.583740,2608.386475,2600.903809,2590.127197,2580.098389,2572.839600</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2638.590088,2640.590088,2634.330078,2633.639893,2587.179932,2584.969971</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>22.006348,32.203613,33.426269,43.512696,7.081543,12.130371</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.834019,1.219561,1.268872,1.652189,0.273717,0.469265</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.9529371244949153</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>2612.286377,2600.650391,2595.527588,2582.640869,2568.953125,2562.366699</t>
@@ -6655,6 +6711,49 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>2594.654053,2578.917725,2563.359619,2547.539795,2531.041992,2519.468994</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:40:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2582.570312,2576.712402,2572.231445,2568.331787,2565.128174,2563.864746</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2578.319580,2571.192383,2567.443359,2561.355225,2555.525879,2554.663818</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2545.934326,2531.329590,2516.669678,2504.549805,2494.233887,2487.261475</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2560.653809,2548.622314,2537.042725,2529.003906,2521.054932,2515.342041</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2849,6 +2849,44 @@
       </c>
       <c r="F64" t="n">
         <v>2563.86474609375</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2659.070068359375</v>
+      </c>
+      <c r="H64" t="n">
+        <v>95.205322265625</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3.580399155271825</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.343225029924243</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:51</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2634.429443359375</v>
       </c>
     </row>
   </sheetData>
@@ -2862,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6741,6 +6779,24 @@
           <t>2582.570312,2576.712402,2572.231445,2568.331787,2565.128174,2563.864746</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2577.870117,2612.479980,2632.969971,2644.090088,2665.219971,2659.070068</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>4.700195,35.767578,60.738526,75.758301,100.091797,95.205322</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.182329,1.369104,2.306845,2.865194,3.755480,3.580399</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>2.343225029924243</v>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>2578.319580,2571.192383,2567.443359,2561.355225,2555.525879,2554.663818</t>
@@ -6754,6 +6810,49 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>2560.653809,2548.622314,2537.042725,2529.003906,2521.054932,2515.342041</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:51</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2653.412842,2648.690430,2646.111084,2641.106445,2635.899414,2634.429443</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2644.250732,2635.368164,2633.755615,2627.726318,2615.525879,2613.099854</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2614.971680,2598.296387,2583.608887,2567.250977,2552.093750,2542.480225</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2632.204346,2619.271240,2608.516113,2598.162109,2585.122803,2578.082031</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,44 @@
       </c>
       <c r="F65" t="n">
         <v>2634.429443359375</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2730.590087890625</v>
+      </c>
+      <c r="H65" t="n">
+        <v>96.16064453125</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3.521606738327168</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.799828456699275</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:52</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2704.4248046875</v>
       </c>
     </row>
   </sheetData>
@@ -2900,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6840,6 +6878,24 @@
           <t>2653.412842,2648.690430,2646.111084,2641.106445,2635.899414,2634.429443</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2724.530029,2755.239990,2762.050049,2775.580078,2738.810059,2730.590088</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>71.117187,106.549560,115.938965,134.473633,102.910645,96.160645</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2.610255,3.867161,4.197569,4.844884,3.757495,3.521607</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>3.799828456699275</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>2644.250732,2635.368164,2633.755615,2627.726318,2615.525879,2613.099854</t>
@@ -6853,6 +6909,49 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>2632.204346,2619.271240,2608.516113,2598.162109,2585.122803,2578.082031</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:52</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2722.216797,2716.184082,2712.520020,2710.561035,2706.215820,2704.424805</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2712.682129,2703.889160,2703.808105,2698.981445,2690.763672,2685.357422</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2677.336914,2658.050781,2641.678711,2625.395020,2609.395020,2595.380859</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2696.409668,2681.176758,2668.686035,2658.993652,2645.394043,2635.550781</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,6 +2925,44 @@
       </c>
       <c r="F66" t="n">
         <v>2704.4248046875</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2780.39990234375</v>
+      </c>
+      <c r="H66" t="n">
+        <v>75.97509765625</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2.732524108931469</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.644499837588266</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:14</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2774.84814453125</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6939,6 +6977,24 @@
           <t>2722.216797,2716.184082,2712.520020,2710.561035,2706.215820,2704.424805</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2741.620117,2743.889893,2751.860107,2753.379883,2773.679932,2780.399902</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>19.403320,27.705811,39.340087,42.818848,67.464112,75.975097</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.707732,1.009727,1.429582,1.555138,2.432296,2.732524</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1.644499837588266</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>2712.682129,2703.889160,2703.808105,2698.981445,2690.763672,2685.357422</t>
@@ -6952,6 +7008,49 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>2696.409668,2681.176758,2668.686035,2658.993652,2645.394043,2635.550781</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:14</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2784.411865,2782.691162,2781.600830,2779.748779,2775.550293,2774.848145</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2776.597412,2772.040039,2775.679688,2770.518311,2763.703369,2758.288086</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2754.376953,2741.857422,2728.537354,2716.560547,2701.245850,2690.323730</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2767.721191,2760.416260,2750.364990,2742.813477,2730.653809,2723.545166</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2963,6 +2963,44 @@
       </c>
       <c r="F67" t="n">
         <v>2774.84814453125</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2674.3798828125</v>
+      </c>
+      <c r="H67" t="n">
+        <v>100.46826171875</v>
+      </c>
+      <c r="I67" t="n">
+        <v>3.756693742890894</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.635721520682849</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:28</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2667.542236328125</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,6 +7076,24 @@
           <t>2784.411865,2782.691162,2781.600830,2779.748779,2775.550293,2774.848145</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2727.419922,2656.100098,2678.100098,2682.530029,2676.179932,2674.379883</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>56.991943,126.591064,103.500732,97.218750,99.370361,100.468262</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2.089592,4.766050,3.864707,3.624144,3.713142,3.756694</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>3.635721520682849</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>2776.597412,2772.040039,2775.679688,2770.518311,2763.703369,2758.288086</t>
@@ -7051,6 +7107,49 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>2767.721191,2760.416260,2750.364990,2742.813477,2730.653809,2723.545166</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:28</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2670.262695,2668.117676,2667.318359,2667.319092,2665.666260,2667.542236</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2665.123047,2659.885742,2660.840820,2662.984131,2655.255371,2656.482666</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2633.159180,2621.097656,2609.032227,2597.900391,2586.841309,2579.016846</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2649.244385,2639.837891,2630.855469,2625.653076,2617.502686,2612.503174</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3001,6 +3001,44 @@
       </c>
       <c r="F68" t="n">
         <v>2667.542236328125</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2681.679931640625</v>
+      </c>
+      <c r="H68" t="n">
+        <v>14.1376953125</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.5271954771966653</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.7071189787374729</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:46</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2675.35009765625</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7137,6 +7175,24 @@
           <t>2670.262695,2668.117676,2667.318359,2667.319092,2665.666260,2667.542236</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2646.669922,2682.620117,2696.120117,2687.350098,2678.250000,2681.679932</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>23.592773,14.502441,28.801758,20.031006,12.583740,14.137696</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.891414,0.540607,1.068267,0.745381,0.469849,0.527195</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.7071189787374729</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>2665.123047,2659.885742,2660.840820,2662.984131,2655.255371,2656.482666</t>
@@ -7150,6 +7206,49 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>2649.244385,2639.837891,2630.855469,2625.653076,2617.502686,2612.503174</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:46</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2682.095703,2681.190918,2678.985840,2678.795410,2676.579590,2675.350098</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2677.094727,2679.040039,2674.575684,2672.774902,2667.744629,2666.222656</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2646.780273,2637.660645,2625.185547,2617.440430,2607.772949,2598.073730</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2661.699707,2655.095215,2644.855957,2643.048340,2635.568848,2628.505859</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3039,6 +3039,44 @@
       </c>
       <c r="F69" t="n">
         <v>2675.35009765625</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2687.800048828125</v>
+      </c>
+      <c r="H69" t="n">
+        <v>12.449951171875</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.4632022823759956</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.5526112214005867</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:35</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2694.49072265625</v>
       </c>
     </row>
   </sheetData>
@@ -3052,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7236,6 +7274,24 @@
           <t>2682.095703,2681.190918,2678.985840,2678.795410,2676.579590,2675.350098</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2717.040039,2686.060059,2692.949951,2691.310059,2687.370117,2687.800049</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>34.944336,4.869141,13.964111,12.514649,10.790527,12.449951</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1.286118,0.181274,0.518543,0.465002,0.401527,0.463202</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.5526112214005867</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>2677.094727,2679.040039,2674.575684,2672.774902,2667.744629,2666.222656</t>
@@ -7249,6 +7305,49 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>2661.699707,2655.095215,2644.855957,2643.048340,2635.568848,2628.505859</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:35</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2687.129883,2690.784180,2691.724609,2693.168457,2692.590820,2694.490723</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2683.954102,2687.003418,2687.722656,2691.066406,2684.253906,2683.631348</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2652.923340,2651.082520,2643.488770,2637.976074,2631.105957,2625.895996</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2666.484375,2667.100098,2662.076660,2660.882324,2655.946289,2652.287109</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,44 @@
       </c>
       <c r="F70" t="n">
         <v>2694.49072265625</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2692.780029296875</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.710693359375</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.06352889358815127</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.1168178499802045</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:34</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2686.710205078125</v>
       </c>
     </row>
   </sheetData>
@@ -3090,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7335,6 +7373,24 @@
           <t>2687.129883,2690.784180,2691.724609,2693.168457,2692.590820,2694.490723</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2688.989990,2692.500000,2683.959961,2695.689941,2695.870117,2692.780029</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1.860107,1.715820,7.764648,2.521484,3.279297,1.710694</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.069175,0.063726,0.289298,0.093538,0.121642,0.063529</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.1168178499802045</v>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>2683.954102,2687.003418,2687.722656,2691.066406,2684.253906,2683.631348</t>
@@ -7348,6 +7404,49 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>2666.484375,2667.100098,2662.076660,2660.882324,2655.946289,2652.287109</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:34</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2691.593262,2689.715820,2689.312744,2689.850586,2687.520996,2686.710205</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2685.715820,2684.001953,2683.697754,2685.506836,2679.033691,2673.086670</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2657.867676,2652.054199,2643.772705,2639.795166,2631.573242,2628.208496</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2673.161377,2669.834961,2664.773193,2663.663086,2657.356934,2653.263672</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3115,6 +3115,44 @@
       </c>
       <c r="F71" t="n">
         <v>2686.710205078125</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2654.14990234375</v>
+      </c>
+      <c r="H71" t="n">
+        <v>32.560302734375</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.226769547026059</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.5597530292825513</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:19</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2655.27587890625</v>
       </c>
     </row>
   </sheetData>
@@ -3128,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7434,6 +7472,24 @@
           <t>2691.593262,2689.715820,2689.312744,2689.850586,2687.520996,2686.710205</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2709.080078,2689.500000,2690.929932,2687.949951,2651.790039,2654.149902</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>17.486816,0.215820,1.617188,1.900635,35.730957,32.560303</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.645489,0.008025,0.060098,0.070709,1.347428,1.226770</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.5597530292825513</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>2685.715820,2684.001953,2683.697754,2685.506836,2679.033691,2673.086670</t>
@@ -7447,6 +7503,49 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>2673.161377,2669.834961,2664.773193,2663.663086,2657.356934,2653.263672</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:19</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2656.050049,2654.643066,2654.992188,2656.493408,2655.234863,2655.275879</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2652.729492,2652.333252,2650.494629,2652.325195,2651.153809,2650.933594</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2621.408691,2615.402832,2609.488037,2607.531494,2600.118408,2596.386230</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2634.895264,2630.020996,2626.877686,2627.242432,2622.189209,2619.627930</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3153,6 +3153,44 @@
       </c>
       <c r="F72" t="n">
         <v>2655.27587890625</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2671.419921875</v>
+      </c>
+      <c r="H72" t="n">
+        <v>16.14404296875</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.6043244207529499</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.6757009355917443</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:29:03</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2672.71533203125</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7533,6 +7571,24 @@
           <t>2656.050049,2654.643066,2654.992188,2656.493408,2655.234863,2655.275879</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2667.989990,2677.870117,2672.409912,2687.350098,2664.159912,2671.419922</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>11.939941,23.227051,17.417724,30.856690,8.925049,16.144043</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.447526,0.867370,0.651761,1.148220,0.335004,0.604324</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.6757009355917443</v>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>2652.729492,2652.333252,2650.494629,2652.325195,2651.153809,2650.933594</t>
@@ -7546,6 +7602,49 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>2634.895264,2630.020996,2626.877686,2627.242432,2622.189209,2619.627930</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:29:03</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2671.719727,2671.651367,2672.457764,2673.488281,2673.235840,2672.715332</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2667.162354,2670.964844,2671.917969,2672.344727,2670.071533,2670.225098</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2644.317871,2639.660156,2633.549561,2630.273193,2626.457520,2620.068115</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2652.856934,2649.891357,2646.451660,2645.388672,2642.374756,2639.261230</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3191,6 +3191,44 @@
       </c>
       <c r="F73" t="n">
         <v>2672.71533203125</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2666.510009765625</v>
+      </c>
+      <c r="H73" t="n">
+        <v>6.205322265625</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.2327132560125068</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.546424106684789</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:37</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2664.4189453125</v>
       </c>
     </row>
   </sheetData>
@@ -3204,7 +3242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7632,6 +7670,24 @@
           <t>2671.719727,2671.651367,2672.457764,2673.488281,2673.235840,2672.715332</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2731.250000,2673.219971,2688.310059,2677.060059,2670.979980,2666.510010</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>59.530273,1.568604,15.852295,3.571778,2.255860,6.205322</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2.179598,0.058678,0.589675,0.133422,0.084458,0.232713</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.546424106684789</v>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>2667.162354,2670.964844,2671.917969,2672.344727,2670.071533,2670.225098</t>
@@ -7645,6 +7701,49 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>2652.856934,2649.891357,2646.451660,2645.388672,2642.374756,2639.261230</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:37</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2666.900391,2665.283691,2666.250000,2667.054199,2665.895508,2664.418945</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2665.486328,2666.210938,2665.063965,2665.636719,2664.026855,2664.052734</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2637.112305,2631.772949,2627.920410,2626.032715,2621.499512,2616.852539</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2647.148926,2643.155762,2641.705566,2641.285645,2637.578125,2634.466797</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,44 @@
       </c>
       <c r="F74" t="n">
         <v>2664.4189453125</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2711.919921875</v>
+      </c>
+      <c r="H74" t="n">
+        <v>47.5009765625</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.751562654167834</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.872057160632587</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:48</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2689.95751953125</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7731,6 +7769,24 @@
           <t>2666.900391,2665.283691,2666.250000,2667.054199,2665.895508,2664.418945</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2696.709961,2681.780029,2668.870117,2683.929932,2693.729980,2711.919922</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>29.809570,16.496338,2.620117,16.875733,27.834472,47.500977</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1.105405,0.615126,0.098173,0.628769,1.033306,1.751563</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.872057160632587</v>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>2665.486328,2666.210938,2665.063965,2665.636719,2664.026855,2664.052734</t>
@@ -7744,6 +7800,49 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>2647.148926,2643.155762,2641.705566,2641.285645,2637.578125,2634.466797</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:48</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2703.826660,2698.492676,2695.303955,2694.169678,2691.929199,2689.957520</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2702.929688,2695.094971,2692.888184,2692.298340,2689.891113,2686.831055</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2665.935791,2657.654785,2651.899658,2651.299072,2646.752441,2645.614258</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2679.518311,2673.322266,2668.510742,2668.328369,2664.628418,2662.861816</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,6 +3267,44 @@
       </c>
       <c r="F75" t="n">
         <v>2689.95751953125</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2731.330078125</v>
+      </c>
+      <c r="H75" t="n">
+        <v>41.37255859375</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1.514740342996236</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.6215916914640203</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:24</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2708.955078125</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7830,6 +7868,24 @@
           <t>2703.826660,2698.492676,2695.303955,2694.169678,2691.929199,2689.957520</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2705.760010,2681.750000,2698.550049,2705.500000,2718.570068,2731.330078</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.933350,16.742676,3.246094,11.330322,26.640869,41.372558</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0.071453,0.624319,0.120290,0.418788,0.979959,1.514740</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.6215916914640203</v>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>2702.929688,2695.094971,2692.888184,2692.298340,2689.891113,2686.831055</t>
@@ -7843,6 +7899,49 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>2679.518311,2673.322266,2668.510742,2668.328369,2664.628418,2662.861816</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:24</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2727.134033,2719.219482,2709.445068,2711.147705,2709.140625,2708.955078</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2725.170654,2717.137451,2708.086182,2712.133545,2708.046875,2703.503662</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2685.604736,2675.251465,2664.894043,2666.139648,2662.126953,2661.564941</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2700.132568,2691.218506,2681.552979,2684.166504,2680.581055,2680.343262</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3305,6 +3305,44 @@
       </c>
       <c r="F76" t="n">
         <v>2708.955078125</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2673.800048828125</v>
+      </c>
+      <c r="H76" t="n">
+        <v>35.155029296875</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.314796493936888</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1.175754756647454</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:13</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2678.89892578125</v>
       </c>
     </row>
   </sheetData>
@@ -3318,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7929,6 +7967,24 @@
           <t>2727.134033,2719.219482,2709.445068,2711.147705,2709.140625,2708.955078</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2746.199951,2696.929932,2667.290039,2668.139893,2681.610107,2673.800049</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>19.065918,22.289550,42.155029,43.007812,27.530518,35.155029</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0.694265,0.826479,1.580444,1.611902,1.026641,1.314796</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1.175754756647454</v>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>2725.170654,2717.137451,2708.086182,2712.133545,2708.046875,2703.503662</t>
@@ -7942,6 +7998,49 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>2700.132568,2691.218506,2681.552979,2684.166504,2680.581055,2680.343262</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:13</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2677.097168,2676.575684,2675.347656,2675.537598,2677.951172,2678.898926</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2680.690430,2678.411133,2679.459961,2678.406250,2678.966797,2677.890625</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2646.301270,2645.310547,2642.044922,2641.666016,2642.307129,2643.794434</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2656.189453,2655.795898,2653.826172,2653.147461,2655.024414,2656.759277</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,6 +3343,44 @@
       </c>
       <c r="F77" t="n">
         <v>2678.89892578125</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2694.320068359375</v>
+      </c>
+      <c r="H77" t="n">
+        <v>15.421142578125</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.5723574848891372</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.3984772653266895</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:35</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2692.31103515625</v>
       </c>
     </row>
   </sheetData>
@@ -3356,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8028,6 +8066,24 @@
           <t>2677.097168,2676.575684,2675.347656,2675.537598,2677.951172,2678.898926</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2684.010010,2681.219971,2685.189941,2686.939941,2694.030029,2694.320068</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>6.912842,4.644287,9.842285,11.402343,16.078857,15.421142</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0.257556,0.173215,0.366540,0.424362,0.596833,0.572357</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.3984772653266895</v>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>2680.690430,2678.411133,2679.459961,2678.406250,2678.966797,2677.890625</t>
@@ -8041,6 +8097,49 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>2656.189453,2655.795898,2653.826172,2653.147461,2655.024414,2656.759277</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:35</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2695.889648,2694.983887,2693.828125,2691.553223,2692.218262,2692.311035</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2694.647461,2693.726562,2695.150879,2692.254395,2689.310059,2688.910645</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2667.451172,2665.033203,2661.281250,2659.095215,2657.775879,2656.625977</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2677.832031,2676.669922,2674.596191,2672.051270,2671.052246,2671.810059</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3381,6 +3381,44 @@
       </c>
       <c r="F78" t="n">
         <v>2692.31103515625</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2697.889892578125</v>
+      </c>
+      <c r="H78" t="n">
+        <v>5.578857421875</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.2067859565811932</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.4817085572594282</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:21</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2694.148193359375</v>
       </c>
     </row>
   </sheetData>
@@ -3394,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8127,6 +8165,24 @@
           <t>2695.889648,2694.983887,2693.828125,2691.553223,2692.218262,2692.311035</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2699.860107,2698.530029,2701.129883,2726.669922,2715.209961,2697.889893</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>3.970459,3.546142,7.301758,35.116699,22.991699,5.578858</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0.147062,0.131410,0.270322,1.287897,0.846774,0.206786</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.4817085572594282</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>2694.647461,2693.726562,2695.150879,2692.254395,2689.310059,2688.910645</t>
@@ -8140,6 +8196,49 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>2677.832031,2676.669922,2674.596191,2672.051270,2671.052246,2671.810059</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:21</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2697.246338,2697.753174,2696.197266,2694.970947,2696.226318,2694.148193</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2696.295166,2698.689697,2696.346680,2689.718506,2693.965332,2689.821045</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2672.989258,2671.006836,2666.739502,2663.664307,2662.885254,2659.972656</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2681.405029,2681.475830,2678.674805,2676.314697,2675.924072,2674.300049</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3419,6 +3419,44 @@
       </c>
       <c r="F79" t="n">
         <v>2694.148193359375</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2694.81005859375</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.661865234375</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.02456073786218482</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.3132367575810284</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:28</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2694.92724609375</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8226,6 +8264,24 @@
           <t>2697.246338,2697.753174,2696.197266,2694.970947,2696.226318,2694.148193</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2717.760010,2696.770020,2708.419922,2709.560059,2698.219971,2694.810059</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>20.513672,0.983154,12.222656,14.589112,1.993653,0.661866</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0.754801,0.036457,0.451284,0.538431,0.073888,0.024561</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.3132367575810284</v>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>2696.295166,2698.689697,2696.346680,2689.718506,2693.965332,2689.821045</t>
@@ -8239,6 +8295,49 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>2681.405029,2681.475830,2678.674805,2676.314697,2675.924072,2674.300049</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:28</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2694.624268,2695.093994,2693.416992,2693.170898,2694.391602,2694.927246</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2693.588623,2695.777344,2693.700439,2692.263428,2693.701172,2690.758301</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2671.072021,2670.035156,2665.947998,2664.099609,2663.717285,2663.407227</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2679.483398,2679.699951,2676.930420,2676.070801,2675.783936,2676.241211</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,44 @@
       </c>
       <c r="F80" t="n">
         <v>2694.92724609375</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2616.2099609375</v>
+      </c>
+      <c r="H80" t="n">
+        <v>78.71728515625</v>
+      </c>
+      <c r="I80" t="n">
+        <v>3.008829043982473</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1.234379445242626</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:41</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2650.32861328125</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8325,6 +8363,24 @@
           <t>2694.624268,2695.093994,2693.416992,2693.170898,2694.391602,2694.927246</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2713.620117,2702.399902,2691.739990,2697.280029,2610.530029,2616.209961</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>18.995849,7.305908,1.677002,4.109131,83.861573,78.717285</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.700019,0.270349,0.062302,0.152344,3.212435,3.008829</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>1.234379445242626</v>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>2693.588623,2695.777344,2693.700439,2692.263428,2693.701172,2690.758301</t>
@@ -8338,6 +8394,49 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>2679.483398,2679.699951,2676.930420,2676.070801,2675.783936,2676.241211</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:41</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2633.921387,2636.437012,2639.612793,2643.111816,2647.001953,2650.328613</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2635.125488,2635.463867,2639.508789,2643.071289,2645.154297,2647.855957</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2595.364258,2591.857422,2588.493652,2588.357422,2586.913086,2587.624512</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2610.481445,2609.098633,2607.816406,2609.204102,2608.911133,2611.515625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3495,44 @@
       </c>
       <c r="F81" t="n">
         <v>2650.32861328125</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2567.89990234375</v>
+      </c>
+      <c r="H81" t="n">
+        <v>82.4287109375</v>
+      </c>
+      <c r="I81" t="n">
+        <v>3.209965889334955</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2.79485921152443</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:54</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2565.7353515625</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,6 +8462,24 @@
           <t>2633.921387,2636.437012,2639.612793,2643.111816,2647.001953,2650.328613</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2577.379883,2569.399902,2569.550049,2572.800049,2562.520020,2567.899902</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>56.541504,67.037110,70.062744,70.311767,84.481933,82.428711</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2.193759,2.609057,2.726654,2.732889,3.296830,3.209966</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>2.79485921152443</v>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>2635.125488,2635.463867,2639.508789,2643.071289,2645.154297,2647.855957</t>
@@ -8437,6 +8493,49 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>2610.481445,2609.098633,2607.816406,2609.204102,2608.911133,2611.515625</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:54</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2567.559082,2568.901855,2568.386719,2567.803223,2568.083984,2565.735352</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2567.906250,2571.797852,2566.626953,2570.733398,2570.096191,2567.913086</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2541.144043,2537.320312,2532.696777,2528.519043,2521.708984,2515.869141</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2552.307617,2549.466797,2545.580078,2541.931152,2538.678711,2535.333984</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,6 +3533,44 @@
       </c>
       <c r="F82" t="n">
         <v>2565.7353515625</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2488.580078125</v>
+      </c>
+      <c r="H82" t="n">
+        <v>77.1552734375</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3.100373346058126</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3.524258377645245</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:58</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2491.55322265625</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8523,6 +8561,24 @@
           <t>2567.559082,2568.901855,2568.386719,2567.803223,2568.083984,2565.735352</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2535.379883,2433.350098,2462.840088,2472.889893,2491.310059,2488.580078</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>32.179199,135.551757,105.546631,94.913330,76.773925,77.155274</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1.269206,5.570582,4.285566,3.838154,3.081669,3.100373</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>3.524258377645245</v>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>2567.906250,2571.797852,2566.626953,2570.733398,2570.096191,2567.913086</t>
@@ -8536,6 +8592,49 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>2552.307617,2549.466797,2545.580078,2541.931152,2538.678711,2535.333984</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:58</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2487.763672,2489.881592,2491.641602,2491.505371,2493.232178,2491.553223</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2485.571289,2493.009033,2490.916748,2494.842773,2495.457764,2497.475342</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2443.984375,2438.546143,2434.666748,2431.396240,2427.674561,2422.266846</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2461.773926,2458.399658,2455.398926,2453.129883,2451.047119,2448.528076</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3571,6 +3571,44 @@
       </c>
       <c r="F83" t="n">
         <v>2491.55322265625</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2494.85009765625</v>
+      </c>
+      <c r="H83" t="n">
+        <v>3.296875</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.1321472181073003</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.3366145193046168</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:21</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2494.0341796875</v>
       </c>
     </row>
   </sheetData>
@@ -3584,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8622,6 +8660,24 @@
           <t>2487.763672,2489.881592,2491.641602,2491.505371,2493.232178,2491.553223</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2504.219971,2487.000000,2474.379883,2485.229980,2489.139893,2494.850098</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>16.456299,2.881592,17.261719,6.275391,4.092285,3.296875</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0.657143,0.115866,0.697618,0.252507,0.164406,0.132147</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.3366145193046168</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>2485.571289,2493.009033,2490.916748,2494.842773,2495.457764,2497.475342</t>
@@ -8635,6 +8691,49 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>2461.773926,2458.399658,2455.398926,2453.129883,2451.047119,2448.528076</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:21</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2495.762695,2496.178223,2496.569824,2495.014160,2496.755859,2494.034180</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2496.523438,2499.652344,2496.747803,2498.525879,2499.295410,2499.553223</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2460.791504,2454.132812,2449.751709,2446.164795,2443.728271,2439.500000</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2475.136230,2470.222900,2466.160156,2463.381836,2461.915039,2459.871094</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3609,6 +3609,44 @@
       </c>
       <c r="F84" t="n">
         <v>2494.0341796875</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2506.090087890625</v>
+      </c>
+      <c r="H84" t="n">
+        <v>12.055908203125</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.4810644382410232</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.3292558499085262</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:31</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2502.5625</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8721,6 +8759,24 @@
           <t>2495.762695,2496.178223,2496.569824,2495.014160,2496.755859,2494.034180</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2494.899902,2509.419922,2510.860107,2503.860107,2497.000000,2506.090088</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0.862793,13.241699,14.290283,8.845947,0.244141,12.055908</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.034582,0.527680,0.569139,0.353292,0.009777,0.481064</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.3292558499085262</v>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>2496.523438,2499.652344,2496.747803,2498.525879,2499.295410,2499.553223</t>
@@ -8734,6 +8790,49 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>2475.136230,2470.222900,2466.160156,2463.381836,2461.915039,2459.871094</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:31</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2504.052246,2503.564209,2503.627930,2502.299316,2504.246826,2502.562500</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2504.550293,2506.273682,2504.214111,2502.694824,2506.649658,2506.988525</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2476.338623,2470.624268,2467.303223,2465.628174,2464.628662,2462.298584</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2487.751465,2483.405518,2480.119141,2478.846680,2478.435791,2478.769775</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,6 +3647,44 @@
       </c>
       <c r="F85" t="n">
         <v>2502.5625</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2555.2099609375</v>
+      </c>
+      <c r="H85" t="n">
+        <v>52.6474609375</v>
+      </c>
+      <c r="I85" t="n">
+        <v>2.060396669641339</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1.203179393267854</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:40</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2555.5302734375</v>
       </c>
     </row>
   </sheetData>
@@ -3660,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8820,6 +8858,24 @@
           <t>2504.052246,2503.564209,2503.627930,2502.299316,2504.246826,2502.562500</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2503.639893,2532.989990,2533.909912,2534.219971,2543.050049,2555.209961</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0.412353,29.425781,30.281982,31.920655,38.803223,52.647461</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.016470,1.161701,1.195069,1.259585,1.525854,2.060397</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>1.203179393267854</v>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>2504.550293,2506.273682,2504.214111,2502.694824,2506.649658,2506.988525</t>
@@ -8833,6 +8889,49 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>2487.751465,2483.405518,2480.119141,2478.846680,2478.435791,2478.769775</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:40</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2553.712646,2554.644531,2554.471680,2554.074951,2555.808594,2555.530273</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2552.001465,2552.145264,2555.905762,2553.761230,2556.639404,2556.569580</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2519.620361,2513.591553,2506.769043,2503.378662,2500.865723,2496.842529</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2534.271484,2530.578125,2525.781494,2523.934814,2521.727539,2520.716553</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,6 +3685,44 @@
       </c>
       <c r="F86" t="n">
         <v>2555.5302734375</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2531.679931640625</v>
+      </c>
+      <c r="H86" t="n">
+        <v>23.850341796875</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.9420757141847338</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.722399527127045</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:54</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2529.328125</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8919,6 +8957,24 @@
           <t>2553.712646,2554.644531,2554.471680,2554.074951,2555.808594,2555.530273</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2543.570068,2527.610107,2518.459961,2444.300049,2505.620117,2531.679932</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>10.142578,27.034424,36.011719,109.774902,50.188477,23.850341</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0.398754,1.069565,1.429910,4.491057,2.003036,0.942076</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1.722399527127045</v>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>2552.001465,2552.145264,2555.905762,2553.761230,2556.639404,2556.569580</t>
@@ -8932,6 +8988,49 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>2534.271484,2530.578125,2525.781494,2523.934814,2521.727539,2520.716553</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:54</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2530.752441,2528.577637,2529.642578,2529.308594,2529.621582,2529.328125</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2528.911621,2527.840332,2531.242188,2529.422363,2530.198242,2531.280273</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2494.227539,2484.030762,2478.992676,2475.447754,2473.003906,2468.148926</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2509.372559,2502.078125,2498.974121,2497.110352,2493.967773,2493.279541</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,6 +3723,44 @@
       </c>
       <c r="F87" t="n">
         <v>2529.328125</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2514.64990234375</v>
+      </c>
+      <c r="H87" t="n">
+        <v>14.67822265625</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.5837083978397682</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.9290475099680333</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:33</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2514.252197265625</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9018,6 +9056,24 @@
           <t>2530.752441,2528.577637,2529.642578,2529.308594,2529.621582,2529.328125</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2497.229980,2513.699951,2505.310059,2495.639893,2511.139893,2514.649902</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>33.522461,14.877686,24.332519,33.668701,18.481689,14.678223</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1.342386,0.591864,0.971238,1.349101,0.735988,0.583708</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0.9290475099680333</v>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>2528.911621,2527.840332,2531.242188,2529.422363,2530.198242,2531.280273</t>
@@ -9031,6 +9087,49 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>2509.372559,2502.078125,2498.974121,2497.110352,2493.967773,2493.279541</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:33</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2510.512207,2511.425049,2513.163086,2512.765625,2514.408203,2514.252197</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2509.278320,2510.821777,2513.765625,2513.164795,2512.258789,2516.220459</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2481.777100,2476.335938,2473.859131,2471.658203,2470.819092,2466.674805</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2494.355713,2490.785156,2489.270996,2488.363037,2486.710938,2486.348877</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3761,6 +3761,44 @@
       </c>
       <c r="F88" t="n">
         <v>2514.252197265625</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2365.5400390625</v>
+      </c>
+      <c r="H88" t="n">
+        <v>148.712158203125</v>
+      </c>
+      <c r="I88" t="n">
+        <v>6.286604992831232</v>
+      </c>
+      <c r="J88" t="n">
+        <v>4.029602732358815</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:19:08</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2391.01708984375</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9117,6 +9155,24 @@
           <t>2510.512207,2511.425049,2513.163086,2512.765625,2514.408203,2514.252197</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2502.020020,2427.149902,2427.929932,2418.550049,2357.110107,2365.540039</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>8.492187,84.275147,85.233154,94.215576,157.298096,148.712158</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.339413,3.472185,3.510528,3.895540,6.673345,6.286605</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>4.029602732358815</v>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>2509.278320,2510.821777,2513.765625,2513.164795,2512.258789,2516.220459</t>
@@ -9130,6 +9186,49 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>2494.355713,2490.785156,2489.270996,2488.363037,2486.710938,2486.348877</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:19:08</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2376.773438,2376.836182,2381.787842,2385.821045,2388.352783,2391.017090</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2373.285645,2378.611816,2383.155518,2388.004395,2389.351074,2389.047363</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2308.774170,2293.192627,2290.056396,2283.286621,2281.893555,2272.190918</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2335.218506,2327.900146,2325.390625,2326.075195,2323.615234,2322.588623</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3799,6 +3799,44 @@
       </c>
       <c r="F89" t="n">
         <v>2391.01708984375</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2436.840087890625</v>
+      </c>
+      <c r="H89" t="n">
+        <v>45.822998046875</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1.880426962548054</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.010470131809917</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:42</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2445.07568359375</v>
       </c>
     </row>
   </sheetData>
@@ -3812,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9216,6 +9254,24 @@
           <t>2376.773438,2376.836182,2381.787842,2385.821045,2388.352783,2391.017090</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2360.139893,2438.139893,2450.570068,2438.689941,2436.810059,2436.840088</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>16.633545,61.303711,68.782226,52.868896,48.457276,45.822998</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0.704769,2.514364,2.806785,2.167922,1.988554,1.880427</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>2.010470131809917</v>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>2373.285645,2378.611816,2383.155518,2388.004395,2389.351074,2389.047363</t>
@@ -9229,6 +9285,49 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>2335.218506,2327.900146,2325.390625,2326.075195,2323.615234,2322.588623</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:42</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2441.207764,2442.169434,2443.552490,2443.066406,2445.430420,2445.075684</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2437.796387,2444.070557,2442.667480,2444.667969,2444.134277,2444.266113</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2396.876221,2390.246826,2387.385742,2384.411621,2383.337646,2379.374512</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2414.342773,2410.784668,2409.549316,2406.833984,2407.152344,2405.978027</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3837,6 +3837,44 @@
       </c>
       <c r="F90" t="n">
         <v>2445.07568359375</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2423.320068359375</v>
+      </c>
+      <c r="H90" t="n">
+        <v>21.755615234375</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.8977607010494444</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1.004900023695911</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:51</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2434.1591796875</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9315,6 +9353,24 @@
           <t>2441.207764,2442.169434,2443.552490,2443.066406,2445.430420,2445.075684</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2474.209961,2428.320068,2409.850098,2419.919922,2424.280029,2423.320068</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>33.002197,13.849366,33.702392,23.146484,21.150391,21.755616</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1.333848,0.570327,1.398527,0.956498,0.872440,0.897761</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>1.004900023695911</v>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>2437.796387,2444.070557,2442.667480,2444.667969,2444.134277,2444.266113</t>
@@ -9328,6 +9384,49 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>2414.342773,2410.784668,2409.549316,2406.833984,2407.152344,2405.978027</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:51</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2426.386963,2428.310059,2431.839844,2432.730225,2435.087646,2434.159180</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2428.061768,2432.619141,2431.397217,2433.964355,2435.057617,2437.684326</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2382.420410,2377.575439,2375.620605,2373.808594,2371.827881,2367.722900</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2400.227051,2397.681641,2398.134277,2396.668945,2397.912354,2396.924072</t>
         </is>
       </c>
     </row>
